--- a/wonderBoy.xlsx
+++ b/wonderBoy.xlsx
@@ -5,17 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WD\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\250616JY\Github\wonderboy2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC121339-F36B-469A-B24A-89CE6C0DCAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E5AE52-610D-4A5C-880E-859AC552B42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{196A970C-7FE6-4DB0-BC1D-10637FB7CC4F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{196A970C-7FE6-4DB0-BC1D-10637FB7CC4F}"/>
   </bookViews>
   <sheets>
-    <sheet name="화면설정" sheetId="2" r:id="rId1"/>
-    <sheet name="wonderBoy" sheetId="1" r:id="rId2"/>
-    <sheet name="Message" sheetId="3" r:id="rId3"/>
+    <sheet name="게임 구성" sheetId="4" r:id="rId1"/>
+    <sheet name="PlayerPrefs" sheetId="5" r:id="rId2"/>
+    <sheet name="화면설정" sheetId="2" r:id="rId3"/>
+    <sheet name="wonderBoy" sheetId="1" r:id="rId4"/>
+    <sheet name="Message" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="144">
   <si>
     <t>최초 게임 설정</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,6 +77,467 @@
   </si>
   <si>
     <t>디스플레이 해상도 변경해도 카메라 사이즈를 자동으로 조정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>씬 : Menu01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Canvas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Image</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> InsertCoinTxt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> CreditTxt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIManager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoinManager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>씬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오브젝트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스크립트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIManagerOne</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIManagerOne.cs에서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작하면 CoinManager 인스턴스 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>using System;</t>
+  </si>
+  <si>
+    <t>using System.Collections;</t>
+  </si>
+  <si>
+    <t>using System.Collections.Generic;</t>
+  </si>
+  <si>
+    <t>using System.Threading;</t>
+  </si>
+  <si>
+    <t>using UnityEngine;</t>
+  </si>
+  <si>
+    <t>using UnityEngine.UI;</t>
+  </si>
+  <si>
+    <t>using UnityEngine.SceneManagement; // 씬 전환에 필요</t>
+  </si>
+  <si>
+    <t>public class UIManagerOne : MonoBehaviour</t>
+  </si>
+  <si>
+    <t>{</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    //InsertCoinView _ Menu01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Text istCoinTxt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public float MenuOneperiod = 0.2f;//깜빡 주기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    private float MenuOnetimer;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Text Credit;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string nextSceneName = "Menu02"; // 전환할 씬 이름    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void Start()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        CoinManager.Instance.ResetCoin();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        istCoinTxt.text = "Insert Coin";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Credit.text = "CREDIT 0";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void Update()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        //InsertCoin 깜빡거림처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        MenuOnetimer += Time.deltaTime;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (MenuOnetimer &gt;= MenuOneperiod)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            istCoinTxt.gameObject.SetActive(!istCoinTxt.gameObject.activeSelf);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            MenuOnetimer = 0f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        //Insert Coin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (Input.GetKeyDown(KeyCode.LeftShift) || Input.GetKeyDown(KeyCode.RightShift))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            CoinManager.Instance.AddCoin(1);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Credit.text = "CREDIT " + CoinManager.Instance.Coin;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            SceneManager.LoadScene(nextSceneName);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        </t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>text 값 조정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetActive -&gt; true, false로 Insert Coin 깜빡거림 처리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shift키 누르면 코인 충전 -&gt; 코인매니저에서 관리 -&gt; 다음씬으로 넘어감</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Menu02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player1Score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player2Score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HIGH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HIGHScore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Credit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Text</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIManagerTwo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>using UnityEngine.SceneManagement;</t>
+  </si>
+  <si>
+    <t>public class UIManagerTwo : MonoBehaviour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    //PUSH START BUTTON ONE OR TWO PLAYERS _ Menu02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Text PlayerOneUI;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Text PlayerTwoUI;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public Text MessageUI;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public float MenuTwoperiod = 1.5f;//깜빡 주기    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string nextSceneName = "Stage01";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        PlayerOneUI.text = "Player 1";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        PlayerTwoUI.text = "Player 2";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        MessageUI.text = "PUSH START BUTTON \r\nONE OR TWO PLAYERS";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Credit.text = "CREDIT " + CoinManager.Instance.Coin;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // Player 1, 2 깜빡 거림 처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         Time.unscaledTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         게임이 시작된 뒤 흐른 실제 시간(초)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         Time.time과 달리 Time.timeScale 영향을 받지 않음 (일시정지해도 계속 증가)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         */</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        float t = Mathf.Repeat(Time.unscaledTime, MenuTwoperiod) / MenuTwoperiod;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        /*         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">         Mathf.Repeat(a, b)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         a를 b로 나눈 나머지를 반환 (0 이상 b 미만)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         즉, MenuTwoperiod마다 값이 0으로 리셋됨 → 주기적인 값 만들기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        / MenuTwoperiod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          0 ~ MenuTwoperiod 구간을 0~1 범위로 정규화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          ➡ 결과적으로 t는 0에서 1까지 반복되는 값이 되고, 한 주기(MenuTwoperiod초)마다 다시 0으로 돌아옴.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        bool on = t &lt; 0.5f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        PlayerOneUI.gameObject.SetActive(on);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        PlayerTwoUI.gameObject.SetActive(!on);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        //Insert Coin -&gt; credit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (CoinManager.Instance.Coin &gt; 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if (Input.GetKeyDown(KeyCode.Return))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                SceneManager.LoadScene(nextSceneName);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            }</t>
+  </si>
+  <si>
+    <t>PlayerOneUI 초기값 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerTwoUI 초기값 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MessageUI 초기값 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Credit 초기값 설정 -&gt; 코인은 코인매니저에서 값 불러오기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인이 1 이상일때 EnterKey를 누르면 Stage01로 씬 전환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> RBlackImg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> LBlackImg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> StateImg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Player1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Player2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> PlayerScore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> HIGHScore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackGround</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MessageContoroller</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MessageTriggerGroup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MessageUI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Panel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> StartTrigger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> MonsterLandTrigger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> SwordRoom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>menu01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoinManager.cs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> coin = PlayerPrefs.GetInt("Coin");</t>
+  </si>
+  <si>
+    <t>PlayerPrefs.SetInt("Coin", coin);</t>
+  </si>
+  <si>
+    <t>Door01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoorManager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coin = PlayerPrefs.GetInt("Coin");</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>availableCount = PlayerPrefs.GetInt($"DoorCount_{doorId}", availableCount);</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PlayerPrefs.GetInt($"DoorCount_{doorId}", availableCount);</t>
+  </si>
+  <si>
+    <t>PlayerPrefs Key Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key값은 문 오브젝트의 이름으로 설정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -82,7 +545,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,6 +562,20 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="굴림"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="굴림"/>
       <family val="3"/>
@@ -133,7 +610,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -141,6 +618,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -161,6 +671,143 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>562714</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>29086</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63E6CCB0-98FC-4A37-9689-0085B42DE123}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2667000" y="142875"/>
+          <a:ext cx="5296639" cy="3658111"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>629494</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>19627</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C58FE0AC-0217-4FFD-A3F0-B656F56B5641}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2905125" y="8915400"/>
+          <a:ext cx="6049219" cy="4134427"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>602169</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>125303</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EB69B29-3A7C-4B4E-8079-6B8E3F2C2FFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4210050" y="21764625"/>
+          <a:ext cx="15003969" cy="10593278"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -947,7 +1594,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1823,7 +2470,7 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">81 542 22 0 0,'0'0'850'0'0,"-8"1"-291"0"0,-20 3-431 0 0,1 0 2415 0 0,9-1 3696 0 0,92 9-6381 0 0,4-9-83 0 0,108-1 225 0 0,-178-2-43 0 0,-2 2-109 0 0,16 5 141 0 0,-22-7 11 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-2 8 4 0 0,0 1 0 0 0,-75 183 21 0 0,21-59-14 0 0,20-43-1 0 0,35-90-18 0 0,-5 14-1967 0 0,0 1 1 0 0,-14 20 0 0 0,15-38 306 0 0,-23-8-229 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="326.92">3 884 262 0 0,'3'-4'423'0'0,"2"-2"-247"0"0,0 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,11 0 0 0 0,39-3 211 0 0,3 5-150 0 0,1 5-72 0 0,27 2-139 0 0,-80-7-289 0 0,0 0-157 0 0,24 1-145 0 0,-24-2-95 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="326.91">3 884 262 0 0,'3'-4'423'0'0,"2"-2"-247"0"0,0 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,11 0 0 0 0,39-3 211 0 0,3 5-150 0 0,1 5-72 0 0,27 2-139 0 0,-80-7-289 0 0,0 0-157 0 0,24 1-145 0 0,-24-2-95 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="655.75">486 337 54 0 0,'-3'-6'443'0'0,"1"2"-868"0"0,-14-32 3349 0 0,13 28-1074 0 0,13 25-1388 0 0,3 15-212 0 0,-1 1 0 0 0,-2 0 0 0 0,-1 0 0 0 0,-2 1-1 0 0,4 35 1 0 0,11 49 346 0 0,20 69 27 0 0,70 255-512 0 0,-108-417-936 0 0,-4-25 800 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-3-3-57 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,-2-5-1 0 0,-4-5 262 0 0,1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,1-1-1 0 0,1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0-1 1 0 0,8-28-1 0 0,-8 41-129 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,7-4 0 0 0,0 1-86 0 0,0 1 1 0 0,1 0 0 0 0,18-7 0 0 0,31-15-3051 0 0,-55 25 2698 0 0,-3 1 190 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,2-3-1 0 0,16-19-2152 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1074.47">924 333 480 0 0,'-15'-44'3806'0'0,"14"41"-904"0"0,3 6-2526 0 0,5 10-149 0 0,-2-1 0 0 0,1 1 0 0 0,-2 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,-1-1 0 0 0,1 25 0 0 0,4 14 321 0 0,14 131 256 0 0,-5-29-693 0 0,-9-88-76 0 0,-6-61-7 0 0,-1-4-24 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,2 0-3 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-2 1 0 0,-31-36-15 0 0,18 17 61 0 0,2 0-1 0 0,1-1 1 0 0,0 0 0 0 0,2-1 0 0 0,0 0 0 0 0,2 0 0 0 0,0-1-1 0 0,-3-30 1 0 0,8 41-76 0 0,2 0 0 0 0,-1-1 0 0 0,2 1 0 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,12-14 0 0 0,-10 10 183 0 0,-6 10-127 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,8-5 0 0 0,14 0-51 0 0,-21 6 96 0 0,1 4-158 0 0,-2 0 70 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 2-1 0 0,0-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,2 6 1 0 0,9 24 197 0 0,-9-23-142 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 27 0 0 0,-3-19-35 0 0,-1 1-1 0 0,-1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,-2 0-1 0 0,0 0 1 0 0,-12 31 0 0 0,14-49-10 0 0,-65 147-414 0 0,65-147 403 0 0,0 1-11 0 0,-5 4-69 0 0,8-21 7 0 0,-1 9 111 0 0,1 1-25 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,5-2 0 0 0,-3 1-4 0 0,8-5 0 0 0,1 1 0 0 0,0 1-1 0 0,0 0 1 0 0,21-6-1 0 0,-28 11-14 0 0,0-1-144 0 0,64-10-3052 0 0,-63 11 2257 0 0,-4-2-17 0 0,0 0 472 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,3-5-1 0 0,-4 5-891 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1417.54">1263 640 222 0 0,'-2'-3'468'0'0,"0"1"-270"0"0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 1 0 0,1-3-1 0 0,0 1-34 0 0,3 1-22 0 0,66-33 96 0 0,-66 34-426 0 0,-1-1 47 0 0,16-8-227 0 0,-16 8-75 0 0,1-1-3 0 0,12-10 7 0 0,-13 10 32 0 0,-3 1 58 0 0,0 2 431 0 0,11-44-1249 0 0,-11 29 4371 0 0,18 233-1722 0 0,-13-116-2211 0 0,-6-68-569 0 0,0-28 449 0 0</inkml:trace>
@@ -1935,8 +2582,8 @@
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8812">3590 806 202 0 0,'0'0'1067'0'0,"-7"-2"231"0"0,-24-7 4023 0 0,25 6-3894 0 0,5 3-1325 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,2-1-58 0 0,3-2 17 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,9-1 0 0 0,45-6 102 0 0,6 1-52 0 0,21 3-33 0 0,-80 5-57 0 0,1 0 39 0 0,24 0-29 0 0,-24 0 19 0 0,-3 3-22 0 0,17 7 38 0 0,-16-7-10 0 0,-7 13 86 0 0,0 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,-9 17-1 0 0,-13 65-42 0 0,26-93-418 0 0,2 15-1652 0 0,21-36-10488 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9154.78">3870 594 104 0 0,'-27'-105'4387'0'0,"25"99"-3532"0"0,1 2-45 0 0,1 3-760 0 0,0 1 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,23 10 936 0 0,-11-1-746 0 0,-1 0 0 0 0,-1 1 0 0 0,1 1 0 0 0,-1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,13 22 0 0 0,6 7-40 0 0,25 32 240 0 0,45 81 0 0 0,-89-138-949 0 0,10 23-393 0 0,-20-37 827 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-3 0 0 0 0,0 1-180 0 0,-3-5 56 0 0,-2 0 282 0 0,1 0-1 0 0,0 0 0 0 0,1-1 0 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,0-1 1 0 0,0-1-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,2 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 0 0 0,0 0 1 0 0,-2-8-1 0 0,3 10 56 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,2-4 0 0 0,0 0 20 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,7-8 0 0 0,-7 10-183 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 2 0 0 0,1-1 0 0 0,7 1 0 0 0,-8 0-120 0 0,-6 0 59 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,2 3 0 0 0,0-1-301 0 0,-3-1 230 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 1 1 0 0,0 8-2696 0 0,-3 20-798 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9498.51">3921 1100 712 0 0,'0'0'3189'0'0,"-6"-2"-1729"0"0,-19-7-76 0 0,25 8-1295 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,1-1 1 0 0,16-11 332 0 0,1 1 1 0 0,0 0-1 0 0,1 2 1 0 0,0 0-1 0 0,34-9 0 0 0,106-22-1174 0 0,-153 39 575 0 0,19-7-929 0 0,-24 8 894 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,2 2 1 0 0,24 1-1046 0 0,-22-2-200 0 0,-7 3-705 0 0,0 16-544 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9838.85">4052 1184 324 0 0,'-30'12'1105'0'0,"24"-10"143"0"0,0-1 26 0 0,-19 4-118 0 0,19-4 3323 0 0,12-4-3865 0 0,160-48 1222 0 0,-100 32-3020 0 0,79-32 0 0 0,-123 45-228 0 0,7-3-315 0 0,-21-3-2398 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9839.85">4122 1078 234 0 0,'-23'14'1459'0'0,"0"0"0"0"0,-38 31 0 0 0,59-42-1192 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 7-1 0 0,1-9-67 0 0,0 0-84 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,1 1 0 0 0,20 11 634 0 0,-16-10-579 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,15-1 0 0 0,-15 0-148 0 0,23 0-41 0 0,0-1-1 0 0,0-2 1 0 0,0-2-1 0 0,-1 0 1 0 0,1-2-1 0 0,44-18 0 0 0,-46 15-887 0 0,0-2 0 0 0,-1 0 0 0 0,33-22 0 0 0,-44 24-94 0 0,0-1-1 0 0,-1 0 0 0 0,0-1 0 0 0,-1-1 1 0 0,0 0-1 0 0,12-18 0 0 0,-9 5-1606 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9838.84">4052 1184 324 0 0,'-30'12'1105'0'0,"24"-10"143"0"0,0-1 26 0 0,-19 4-118 0 0,19-4 3323 0 0,12-4-3865 0 0,160-48 1222 0 0,-100 32-3020 0 0,79-32 0 0 0,-123 45-228 0 0,7-3-315 0 0,-21-3-2398 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9839.84">4122 1078 234 0 0,'-23'14'1459'0'0,"0"0"0"0"0,-38 31 0 0 0,59-42-1192 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 7-1 0 0,1-9-67 0 0,0 0-84 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,1 1 0 0 0,20 11 634 0 0,-16-10-579 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,15-1 0 0 0,-15 0-148 0 0,23 0-41 0 0,0-1-1 0 0,0-2 1 0 0,0-2-1 0 0,-1 0 1 0 0,1-2-1 0 0,44-18 0 0 0,-46 15-887 0 0,0-2 0 0 0,-1 0 0 0 0,33-22 0 0 0,-44 24-94 0 0,0-1-1 0 0,-1 0 0 0 0,0-1 0 0 0,-1-1 1 0 0,0 0-1 0 0,12-18 0 0 0,-9 5-1606 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10180.68">4559 643 250 0 0,'-18'-3'224'0'0,"13"1"-67"0"0,0 2 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-8 2 0 0 0,2-2 128 0 0,7-1-143 0 0,0 1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-6 3 1 0 0,0-1 154 0 0,1 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,0 0 1 0 0,1 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1-1 0 0,0 0 1 0 0,-9 13 0 0 0,15-19-249 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 2 0 0 0,0 1 112 0 0,-1-3-115 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,3 1 0 0 0,0 1 69 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,7 1-1 0 0,-8-1-43 0 0,10 1 212 0 0,-12-1-251 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,4-3 0 0 0,1 1 118 0 0,1 0-96 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,13-10 0 0 0,-17 11-50 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-9 0 0 0,-2 10-189 0 0,0-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-5-3 1 0 0,-10-12-1697 0 0,-10-11-1893 0 0,4 5 1041 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10181.68">4677 366 686 0 0,'0'0'1580'0'0,"6"3"170"0"0,3 3-904 0 0,0 0-1 0 0,-1 1 0 0 0,1 1 0 0 0,-2-1 0 0 0,1 1 1 0 0,-1 1-1 0 0,0-1 0 0 0,6 11 0 0 0,97 133 4697 0 0,-57-83-4042 0 0,76 75-1 0 0,-105-120-1211 0 0,9 8-850 0 0,32 41 0 0 0,-58-65-46 0 0,0 1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,3 12 1 0 0,-6-17-128 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,-4 6-1 0 0,-5 14-4971 0 0</inkml:trace>
 </inkml:ink>
@@ -2165,7 +2812,7 @@
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="327.19">1047 2778 452 0 0,'-7'-22'1776'0'0,"0"-10"456"0"0,10 2-1308 0 0,20 11-272 0 0,27 2-400 0 0,-14 11-58 0 0,1-2-162 0 0,3 3-356 0 0,-4 0-278 0 0,9-2-226 0 0,-5 1-344 0 0,-4-5-388 0 0,-3-2-142 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="808.56">1390 1928 228 0 0,'-5'-4'750'0'0,"-17"-8"96"0"0,16 8 594 0 0,9 0-884 0 0,0 1-453 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,8 0 1 0 0,-1-1-14 0 0,1 1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,18 4 0 0 0,52 21 459 0 0,-75-18-282 0 0,-6-3-184 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,-3 6 0 0 0,-27 41 707 0 0,-72 87-1 0 0,50-70-442 0 0,-20 10-54 0 0,71-74-199 0 0,4-3-92 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,2 0 1 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,6-1 0 0 0,53 1 6 0 0,8-6 19 0 0,5 4-17 0 0,-61 1-8 0 0,45 3 1 0 0,-47-2 1 0 0,38 7-21 0 0,-43-6 19 0 0,0 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,-1 1 0 0 0,10 6-1 0 0,-15-9 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 6-1 0 0,-3 4 4 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-2-1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,-17 12 0 0 0,-2 2-12 0 0,-2-3 1 0 0,-1 0 0 0 0,-1-2 0 0 0,-36 15 0 0 0,20-15 25 0 0,-1-2 0 0 0,0-2-1 0 0,-75 11 1 0 0,118-25 1 0 0,0 0-65 0 0,-22 2 83 0 0,22-2-48 0 0,25-13 159 0 0,1 3-81 0 0,0 0 1 0 0,1 1 0 0 0,0 1-1 0 0,1 1 1 0 0,26-4 0 0 0,5-3 55 0 0,165-46 232 0 0,-67 19-1830 0 0,-56 13-2856 0 0,-79 22 1655 0 0,18-11-747 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4390.45">1772 1843 330 0 0,'-6'2'565'0'0,"-21"3"103"0"0,20-4-20 0 0,-1 1-2 0 0,0 0-362 0 0,-8 2-112 0 0,1-4 2590 0 0,26 3-2692 0 0,-12 1-48 0 0,1-4-22 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,62 10 149 0 0,33-1-41 0 0,-25-2-71 0 0,-66-6-34 0 0,14 2 7 0 0,0 0 0 0 0,0 2 1 0 0,18 7-1 0 0,-36-12-9 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 1 0 0 0,-6 42 24 0 0,7-43-24 0 0,-11 31 93 0 0,-1 0-1 0 0,-2-1 0 0 0,-2-1 1 0 0,-24 39-1 0 0,18-31-96 0 0,13-17-463 0 0,9-17 340 0 0,-1 0-335 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4716.97">2050 1686 176 0 0,'-24'-12'506'0'0,"19"10"1421"0"0,7 9-1509 0 0,9 21-135 0 0,1-1 1 0 0,2 0-1 0 0,1 0 1 0 0,23 31 0 0 0,-12-19-50 0 0,24 50 0 0 0,11 54 120 0 0,-32-71-371 0 0,63 112-1 0 0,-32-81-1615 0 0,-59-103 1580 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,-2 1 1 0 0,0 0 36 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-1-2 1 0 0,-35-32 1382 0 0,-65-77 0 0 0,101 111-1299 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,2-3 0 0 0,0 1-26 0 0,1 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,8-1 0 0 0,-1 0-8 0 0,35-4-12 0 0,23 2-906 0 0,-4 2-1214 0 0,-24 0 516 0 0,-30 2-178 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4716.96">2050 1686 176 0 0,'-24'-12'506'0'0,"19"10"1421"0"0,7 9-1509 0 0,9 21-135 0 0,1-1 1 0 0,2 0-1 0 0,1 0 1 0 0,23 31 0 0 0,-12-19-50 0 0,24 50 0 0 0,11 54 120 0 0,-32-71-371 0 0,63 112-1 0 0,-32-81-1615 0 0,-59-103 1580 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,-2 1 1 0 0,0 0 36 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-1-2 1 0 0,-35-32 1382 0 0,-65-77 0 0 0,101 111-1299 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,2-3 0 0 0,0 1-26 0 0,1 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,8-1 0 0 0,-1 0-8 0 0,35-4-12 0 0,23 2-906 0 0,-4 2-1214 0 0,-24 0 516 0 0,-30 2-178 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5046.08">2762 1475 220 0 0,'-8'0'847'0'0,"-15"-1"3725"0"0,58 1-3601 0 0,77 8-898 0 0,-101-6 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 2-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,12 11-1 0 0,-15-12 4 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-2-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,-1 11-1 0 0,-1 3 26 0 0,0 0 0 0 0,-2 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,-1 0-1 0 0,-12 24 1 0 0,15-34-194 0 0,0 0-1 0 0,1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 21 1 0 0,-3 16-3605 0 0,4-43 1429 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5403.1">3075 1311 80 0 0,'-6'-3'885'0'0,"-49"-22"2466"0"0,50 23-2498 0 0,6 13-474 0 0,0-1 0 0 0,0 1 0 0 0,1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,0-1 0 0 0,9 15 1 0 0,9 12-120 0 0,29 36 0 0 0,-17-26-38 0 0,12 17-54 0 0,52 80-1160 0 0,-88-125 367 0 0,-1 0 1 0 0,0 1-1 0 0,-2-1 1 0 0,0 2-1 0 0,-1-1 0 0 0,6 29 1 0 0,-11-12-1291 0 0,-5 0-351 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5731.33">2914 2169 384 0 0,'-4'-2'874'0'0,"-12"-7"17"0"0,12 7 756 0 0,8-3-929 0 0,4-3-509 0 0,1 1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,19-5 0 0 0,112-24 659 0 0,-116 28-758 0 0,229-32 1052 0 0,-242 36-1025 0 0,-4 1-129 0 0,23 3 95 0 0,-30-3-103 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-2 1 0 0 0,-48 39-151 0 0,-2-3-1 0 0,-86 48 1 0 0,-10 7 657 0 0,145-90-441 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,0 1-1 0 0,1 0 1 0 0,-2 5 0 0 0,3-8-55 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,2 0-1 0 0,6 5 18 0 0,-6-5-17 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,2-1 0 0 0,1 0 17 0 0,-1 2-16 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,6-1 0 0 0,1 0 1 0 0,-1 2-8 0 0,0-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,15-6 0 0 0,1 0-57 0 0,-1-1-707 0 0,-1 0-1 0 0,1-2 0 0 0,-1 0 1 0 0,-1-2-1 0 0,0 0 0 0 0,-1-1 0 0 0,-1-1 1 0 0,0-1-1 0 0,30-33 0 0 0,-19 13-2015 0 0</inkml:trace>
@@ -2180,7 +2827,7 @@
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8176.69">5508 657 322 0 0,'-75'-16'3632'0'0,"69"15"-1649"0"0,7-1-1869 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,3-1 1 0 0,37-11 476 0 0,-36 11-554 0 0,308-71 328 0 0,-306 71-848 0 0,-11 6-2150 0 0,-10 8 2464 0 0,0 0 1 0 0,-1-1-1 0 0,-1-1 0 0 0,0 0 1 0 0,0-1-1 0 0,-1-1 1 0 0,-19 8-1 0 0,-49 29-51 0 0,-64 59 628 0 0,142-100-282 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 11 1 0 0,3-12 4 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,9 7 0 0 0,-1-3 28 0 0,0-1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0-1 0 0 0,1 0 0 0 0,21-2 0 0 0,-16 0-104 0 0,0-1 0 0 0,0-1 0 0 0,0-1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0-2 0 0 0,0 0 0 0 0,-1-1 0 0 0,24-14 0 0 0,-30 14-232 0 0,0-1-1 0 0,0 1 1 0 0,-1-2-1 0 0,13-13 1 0 0,-19 19-109 0 0,-1-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-2 0-1 0 0,1 0 1 0 0,1-6 0 0 0,-3 6-77 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,-5-5-1 0 0,-7-10-1427 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8723.22">5716 675 232 0 0,'-6'-4'500'0'0,"-47"-31"1957"0"0,54 35-2425 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-7 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,2-1-1 0 0,9-7 151 0 0,1 0 1 0 0,0 1-1 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0 1 1 0 0,19-4-1 0 0,115-18 371 0 0,-130 24-479 0 0,-8 1-3 0 0,46 0 15 0 0,-44 0-50 0 0,-12 6 0 0 0,0 0-25 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-4 4 1 0 0,-46 42 13 0 0,2-4-12 0 0,-14 15 24 0 0,50-49 6 0 0,1 1 1 0 0,0 0 0 0 0,1 1-1 0 0,1 0 1 0 0,0 1-1 0 0,-17 28 1 0 0,28-42-27 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 1 0 0,1 3-1 0 0,-1 1 27 0 0,0-4-25 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,2 1 0 0 0,-2-1 31 0 0,0 1-24 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,4 1-1 0 0,-1 0 45 0 0,11 3 150 0 0,85 0 440 0 0,-80-5-581 0 0,-1 0 1 0 0,1-1 0 0 0,-1-1 0 0 0,0-1-1 0 0,0-1 1 0 0,0-1 0 0 0,-1 0-1 0 0,0-1 1 0 0,0-1 0 0 0,19-12 0 0 0,-2-2 15 0 0,0-1-1 0 0,-1-2 1 0 0,37-37 0 0 0,-70 61-89 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 9 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,63-45-70 0 0,-62 46 57 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,2 4 0 0 0,12 26-17 0 0,-3-2 19 0 0,-8-22-21 0 0,2-27-92 0 0,-4 12 75 0 0,0 3 14 0 0,33-143-1470 0 0,-28 127 1222 0 0,1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,23-36-1 0 0,-28 52 253 0 0,0 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,8-3 0 0 0,-5 2 3 0 0,-2 1-5 0 0,16 0 70 0 0,-18 2 1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 1 0 0,3 2-1 0 0,26 15 544 0 0,0 2 0 0 0,-2 1-1 0 0,32 27 1 0 0,88 84-94 0 0,-99-85-636 0 0,-35-33 158 0 0,-15-13-323 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-2 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 2 0 0 0,0 0-2696 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9440.99">6737 560 68 0 0,'0'0'4044'0'0,"3"-3"-3393"0"0,1-1-420 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 1 0 0 0,9-4 0 0 0,11-4 124 0 0,34-17 122 0 0,-14 7-743 0 0,65-40 1 0 0,-86 39-1124 0 0,-24 20 1222 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-2-1 0 0,-8-20-1245 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9767.46">6945 19 272 0 0,'0'0'895'0'0,"-3"-3"129"0"0,-12-10 18 0 0,12 10-110 0 0,2 7-45 0 0,1 2-613 0 0,-1 0 1 0 0,1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,4 8 0 0 0,34 67 1160 0 0,-22-48-997 0 0,167 275 1898 0 0,27-13-1595 0 0,-118-168-659 0 0,-78-105-432 0 0,50 75-4434 0 0,-65-96 4593 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 1 0 0 0,1 1-566 0 0,0 2-2466 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9767.45">6945 19 272 0 0,'0'0'895'0'0,"-3"-3"129"0"0,-12-10 18 0 0,12 10-110 0 0,2 7-45 0 0,1 2-613 0 0,-1 0 1 0 0,1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,4 8 0 0 0,34 67 1160 0 0,-22-48-997 0 0,167 275 1898 0 0,27-13-1595 0 0,-118-168-659 0 0,-78-105-432 0 0,50 75-4434 0 0,-65-96 4593 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 1 0 0 0,1 1-566 0 0,0 2-2466 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -2512,6 +3159,943 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7548165A-6831-4F75-8F1D-60395F2BCA11}">
+  <dimension ref="A2:N152"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="16.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A5" s="6"/>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A6" s="6"/>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A7" s="6"/>
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A8" s="6"/>
+      <c r="M8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A9" s="6"/>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A10" s="6"/>
+      <c r="M10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A11" s="6"/>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A12" s="7"/>
+      <c r="M12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="M17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="M18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="M20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="M21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="M22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="M23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="M24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="M25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B26" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B29" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="M29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="M30" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B31" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="M31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="M32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M35" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M37" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M38" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M39" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M43" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="5"/>
+      <c r="B48" s="5"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N52" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B54" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="N54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B55" s="6"/>
+      <c r="C55" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N55" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B56" s="6"/>
+      <c r="C56" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="N56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B57" s="6"/>
+      <c r="C57" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="N57" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B58" s="6"/>
+      <c r="C58" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="N58" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B59" s="6"/>
+      <c r="C59" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B60" s="6"/>
+      <c r="C60" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="N60" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B61" s="6"/>
+      <c r="C61" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B63" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N63" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="N64" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="N65" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N66" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="N67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="N68" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="N69" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="N72" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="N73" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="N75" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="N76" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="N77" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="N78" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B79" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="N79" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B80" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B81" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="N81" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="82" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B82" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="N82" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="83" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B83" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="N83" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="84" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B84" s="4"/>
+      <c r="N84" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="85" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B85" s="4"/>
+      <c r="N85" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="86" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B86" s="4"/>
+      <c r="N86" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="87" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B87" s="4"/>
+      <c r="N87" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="88" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B88" s="4"/>
+      <c r="N88" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="89" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B89" s="4"/>
+      <c r="N89" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="90" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B90" s="4"/>
+      <c r="N90" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="91" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B91" s="4"/>
+      <c r="N91" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="92" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B92" s="4"/>
+      <c r="N92" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="93" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B93" s="4"/>
+      <c r="N93" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="94" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B94" s="4"/>
+    </row>
+    <row r="95" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B95" s="4"/>
+      <c r="N95" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="96" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B96" s="4"/>
+      <c r="N96" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="97" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B97" s="4"/>
+      <c r="N97" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="98" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B98" s="4"/>
+      <c r="N98" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="99" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B99" s="4"/>
+    </row>
+    <row r="100" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B100" s="4"/>
+      <c r="N100" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B101" s="4"/>
+      <c r="N101" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B102" s="4"/>
+      <c r="N102" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B103" s="4"/>
+    </row>
+    <row r="104" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B104" s="4"/>
+    </row>
+    <row r="105" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B105" s="4"/>
+      <c r="N105" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="106" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B106" s="4"/>
+      <c r="N106" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="107" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B107" s="4"/>
+      <c r="N107" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="108" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B108" s="4"/>
+      <c r="N108" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="109" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B109" s="4"/>
+      <c r="N109" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="110" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B110" s="4"/>
+      <c r="N110" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="111" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B111" s="4"/>
+    </row>
+    <row r="112" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B112" s="4"/>
+      <c r="N112" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B113" s="4"/>
+      <c r="N113" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B114" s="4"/>
+      <c r="N114" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B115" s="4"/>
+      <c r="N115" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B116" s="4"/>
+      <c r="N116" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B117" s="4"/>
+      <c r="N117" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B118" s="4"/>
+      <c r="N118" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B119" s="4"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B120" s="4"/>
+      <c r="N120" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B121" s="4"/>
+      <c r="N121" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B122" s="4"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B123" s="4"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B124" s="4"/>
+    </row>
+    <row r="125" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A125" s="5"/>
+      <c r="B125" s="8"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B126" s="4"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A127" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B128" s="4"/>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A129" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B130" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B131" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B132" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B133" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B134" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B135" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B136" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B137" s="4"/>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B138" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B139" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B140" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B141" s="4"/>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B142" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B143" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B145" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B146" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B147" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B148" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B150" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B151" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B152" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B54:B61"/>
+    <mergeCell ref="A4:A11"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1E4E7D2-C400-4FA7-B4EE-FE9CDA191CED}">
+  <dimension ref="A2:G11"/>
+  <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="15.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="29.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="124.25" style="10" customWidth="1"/>
+    <col min="5" max="5" width="105.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A3" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E4" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E5" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A8" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E9" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A55F660C-EF88-4090-AD81-2A0B2E837B2C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -2522,7 +4106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32871931-A659-4325-B8EE-1625B1A3CB77}">
   <dimension ref="A1:H225"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -2586,7 +4170,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E919AACA-485F-464F-B192-8B7CCA645328}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>

--- a/wonderBoy.xlsx
+++ b/wonderBoy.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\250616JY\Github\wonderboy2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E5AE52-610D-4A5C-880E-859AC552B42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DC1B57-BF2F-450A-A746-9048B01775D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{196A970C-7FE6-4DB0-BC1D-10637FB7CC4F}"/>
   </bookViews>
   <sheets>
     <sheet name="게임 구성" sheetId="4" r:id="rId1"/>
-    <sheet name="PlayerPrefs" sheetId="5" r:id="rId2"/>
-    <sheet name="화면설정" sheetId="2" r:id="rId3"/>
-    <sheet name="wonderBoy" sheetId="1" r:id="rId4"/>
-    <sheet name="Message" sheetId="3" r:id="rId5"/>
+    <sheet name="UI_Item" sheetId="6" r:id="rId2"/>
+    <sheet name="PlayerPrefs" sheetId="5" r:id="rId3"/>
+    <sheet name="화면설정" sheetId="2" r:id="rId4"/>
+    <sheet name="wonderBoy" sheetId="1" r:id="rId5"/>
+    <sheet name="Message" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="149">
   <si>
     <t>최초 게임 설정</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -538,6 +539,26 @@
   </si>
   <si>
     <t>Key값은 문 오브젝트의 이름으로 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item01 &lt;- IMG 오브젝트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item01SlotUI.cs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryUIController &lt;- 빈 오브젝트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryUIController.cs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI Item01 슬롯창에서 보유하고 있는 아이템을 그려줄 IMG Sprite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -545,7 +566,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -581,6 +602,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -610,7 +638,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -627,9 +655,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -651,6 +676,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2470,7 +2504,7 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">81 542 22 0 0,'0'0'850'0'0,"-8"1"-291"0"0,-20 3-431 0 0,1 0 2415 0 0,9-1 3696 0 0,92 9-6381 0 0,4-9-83 0 0,108-1 225 0 0,-178-2-43 0 0,-2 2-109 0 0,16 5 141 0 0,-22-7 11 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-2 8 4 0 0,0 1 0 0 0,-75 183 21 0 0,21-59-14 0 0,20-43-1 0 0,35-90-18 0 0,-5 14-1967 0 0,0 1 1 0 0,-14 20 0 0 0,15-38 306 0 0,-23-8-229 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="326.91">3 884 262 0 0,'3'-4'423'0'0,"2"-2"-247"0"0,0 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,11 0 0 0 0,39-3 211 0 0,3 5-150 0 0,1 5-72 0 0,27 2-139 0 0,-80-7-289 0 0,0 0-157 0 0,24 1-145 0 0,-24-2-95 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="326.9">3 884 262 0 0,'3'-4'423'0'0,"2"-2"-247"0"0,0 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,11 0 0 0 0,39-3 211 0 0,3 5-150 0 0,1 5-72 0 0,27 2-139 0 0,-80-7-289 0 0,0 0-157 0 0,24 1-145 0 0,-24-2-95 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="655.75">486 337 54 0 0,'-3'-6'443'0'0,"1"2"-868"0"0,-14-32 3349 0 0,13 28-1074 0 0,13 25-1388 0 0,3 15-212 0 0,-1 1 0 0 0,-2 0 0 0 0,-1 0 0 0 0,-2 1-1 0 0,4 35 1 0 0,11 49 346 0 0,20 69 27 0 0,70 255-512 0 0,-108-417-936 0 0,-4-25 800 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-3-3-57 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,-2-5-1 0 0,-4-5 262 0 0,1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,1-1-1 0 0,1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0-1 1 0 0,8-28-1 0 0,-8 41-129 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,7-4 0 0 0,0 1-86 0 0,0 1 1 0 0,1 0 0 0 0,18-7 0 0 0,31-15-3051 0 0,-55 25 2698 0 0,-3 1 190 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,2-3-1 0 0,16-19-2152 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1074.47">924 333 480 0 0,'-15'-44'3806'0'0,"14"41"-904"0"0,3 6-2526 0 0,5 10-149 0 0,-2-1 0 0 0,1 1 0 0 0,-2 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,-1-1 0 0 0,1 25 0 0 0,4 14 321 0 0,14 131 256 0 0,-5-29-693 0 0,-9-88-76 0 0,-6-61-7 0 0,-1-4-24 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,2 0-3 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-2 1 0 0,-31-36-15 0 0,18 17 61 0 0,2 0-1 0 0,1-1 1 0 0,0 0 0 0 0,2-1 0 0 0,0 0 0 0 0,2 0 0 0 0,0-1-1 0 0,-3-30 1 0 0,8 41-76 0 0,2 0 0 0 0,-1-1 0 0 0,2 1 0 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,12-14 0 0 0,-10 10 183 0 0,-6 10-127 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,8-5 0 0 0,14 0-51 0 0,-21 6 96 0 0,1 4-158 0 0,-2 0 70 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 2-1 0 0,0-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,2 6 1 0 0,9 24 197 0 0,-9-23-142 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 27 0 0 0,-3-19-35 0 0,-1 1-1 0 0,-1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,-2 0-1 0 0,0 0 1 0 0,-12 31 0 0 0,14-49-10 0 0,-65 147-414 0 0,65-147 403 0 0,0 1-11 0 0,-5 4-69 0 0,8-21 7 0 0,-1 9 111 0 0,1 1-25 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,5-2 0 0 0,-3 1-4 0 0,8-5 0 0 0,1 1 0 0 0,0 1-1 0 0,0 0 1 0 0,21-6-1 0 0,-28 11-14 0 0,0-1-144 0 0,64-10-3052 0 0,-63 11 2257 0 0,-4-2-17 0 0,0 0 472 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,3-5-1 0 0,-4 5-891 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1417.54">1263 640 222 0 0,'-2'-3'468'0'0,"0"1"-270"0"0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 1 0 0,1-3-1 0 0,0 1-34 0 0,3 1-22 0 0,66-33 96 0 0,-66 34-426 0 0,-1-1 47 0 0,16-8-227 0 0,-16 8-75 0 0,1-1-3 0 0,12-10 7 0 0,-13 10 32 0 0,-3 1 58 0 0,0 2 431 0 0,11-44-1249 0 0,-11 29 4371 0 0,18 233-1722 0 0,-13-116-2211 0 0,-6-68-569 0 0,0-28 449 0 0</inkml:trace>
@@ -2827,7 +2861,7 @@
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8176.69">5508 657 322 0 0,'-75'-16'3632'0'0,"69"15"-1649"0"0,7-1-1869 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,3-1 1 0 0,37-11 476 0 0,-36 11-554 0 0,308-71 328 0 0,-306 71-848 0 0,-11 6-2150 0 0,-10 8 2464 0 0,0 0 1 0 0,-1-1-1 0 0,-1-1 0 0 0,0 0 1 0 0,0-1-1 0 0,-1-1 1 0 0,-19 8-1 0 0,-49 29-51 0 0,-64 59 628 0 0,142-100-282 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 11 1 0 0,3-12 4 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,9 7 0 0 0,-1-3 28 0 0,0-1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0-1 0 0 0,1 0 0 0 0,21-2 0 0 0,-16 0-104 0 0,0-1 0 0 0,0-1 0 0 0,0-1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0-2 0 0 0,0 0 0 0 0,-1-1 0 0 0,24-14 0 0 0,-30 14-232 0 0,0-1-1 0 0,0 1 1 0 0,-1-2-1 0 0,13-13 1 0 0,-19 19-109 0 0,-1-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-2 0-1 0 0,1 0 1 0 0,1-6 0 0 0,-3 6-77 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,-5-5-1 0 0,-7-10-1427 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8723.22">5716 675 232 0 0,'-6'-4'500'0'0,"-47"-31"1957"0"0,54 35-2425 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-7 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,2-1-1 0 0,9-7 151 0 0,1 0 1 0 0,0 1-1 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0 1 1 0 0,19-4-1 0 0,115-18 371 0 0,-130 24-479 0 0,-8 1-3 0 0,46 0 15 0 0,-44 0-50 0 0,-12 6 0 0 0,0 0-25 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-4 4 1 0 0,-46 42 13 0 0,2-4-12 0 0,-14 15 24 0 0,50-49 6 0 0,1 1 1 0 0,0 0 0 0 0,1 1-1 0 0,1 0 1 0 0,0 1-1 0 0,-17 28 1 0 0,28-42-27 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 1 0 0,1 3-1 0 0,-1 1 27 0 0,0-4-25 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,2 1 0 0 0,-2-1 31 0 0,0 1-24 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,4 1-1 0 0,-1 0 45 0 0,11 3 150 0 0,85 0 440 0 0,-80-5-581 0 0,-1 0 1 0 0,1-1 0 0 0,-1-1 0 0 0,0-1-1 0 0,0-1 1 0 0,0-1 0 0 0,-1 0-1 0 0,0-1 1 0 0,0-1 0 0 0,19-12 0 0 0,-2-2 15 0 0,0-1-1 0 0,-1-2 1 0 0,37-37 0 0 0,-70 61-89 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 9 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,63-45-70 0 0,-62 46 57 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,2 4 0 0 0,12 26-17 0 0,-3-2 19 0 0,-8-22-21 0 0,2-27-92 0 0,-4 12 75 0 0,0 3 14 0 0,33-143-1470 0 0,-28 127 1222 0 0,1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,23-36-1 0 0,-28 52 253 0 0,0 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,8-3 0 0 0,-5 2 3 0 0,-2 1-5 0 0,16 0 70 0 0,-18 2 1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 1 0 0,3 2-1 0 0,26 15 544 0 0,0 2 0 0 0,-2 1-1 0 0,32 27 1 0 0,88 84-94 0 0,-99-85-636 0 0,-35-33 158 0 0,-15-13-323 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-2 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 2 0 0 0,0 0-2696 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9440.99">6737 560 68 0 0,'0'0'4044'0'0,"3"-3"-3393"0"0,1-1-420 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 1 0 0 0,9-4 0 0 0,11-4 124 0 0,34-17 122 0 0,-14 7-743 0 0,65-40 1 0 0,-86 39-1124 0 0,-24 20 1222 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-2-1 0 0,-8-20-1245 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9767.45">6945 19 272 0 0,'0'0'895'0'0,"-3"-3"129"0"0,-12-10 18 0 0,12 10-110 0 0,2 7-45 0 0,1 2-613 0 0,-1 0 1 0 0,1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,4 8 0 0 0,34 67 1160 0 0,-22-48-997 0 0,167 275 1898 0 0,27-13-1595 0 0,-118-168-659 0 0,-78-105-432 0 0,50 75-4434 0 0,-65-96 4593 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 1 0 0 0,1 1-566 0 0,0 2-2466 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9767.44">6945 19 272 0 0,'0'0'895'0'0,"-3"-3"129"0"0,-12-10 18 0 0,12 10-110 0 0,2 7-45 0 0,1 2-613 0 0,-1 0 1 0 0,1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,4 8 0 0 0,34 67 1160 0 0,-22-48-997 0 0,167 275 1898 0 0,27-13-1595 0 0,-118-168-659 0 0,-78-105-432 0 0,50 75-4434 0 0,-65-96 4593 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 1 0 0 0,1 1-566 0 0,0 2-2466 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -3185,7 +3219,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="13" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -3196,7 +3230,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="6"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
@@ -3205,7 +3239,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A6" s="6"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
@@ -3214,7 +3248,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A7" s="6"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -3223,25 +3257,25 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="6"/>
+      <c r="A8" s="13"/>
       <c r="M8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A9" s="6"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A10" s="6"/>
+      <c r="A10" s="13"/>
       <c r="M10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11" s="6"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
@@ -3250,7 +3284,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A12" s="7"/>
+      <c r="A12" s="6"/>
       <c r="M12" t="s">
         <v>32</v>
       </c>
@@ -3460,7 +3494,7 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C54" s="4" t="s">
@@ -3471,7 +3505,7 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B55" s="6"/>
+      <c r="B55" s="13"/>
       <c r="C55" s="4" t="s">
         <v>64</v>
       </c>
@@ -3480,7 +3514,7 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B56" s="6"/>
+      <c r="B56" s="13"/>
       <c r="C56" s="4" t="s">
         <v>65</v>
       </c>
@@ -3489,7 +3523,7 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B57" s="6"/>
+      <c r="B57" s="13"/>
       <c r="C57" s="4" t="s">
         <v>66</v>
       </c>
@@ -3498,7 +3532,7 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B58" s="6"/>
+      <c r="B58" s="13"/>
       <c r="C58" s="4" t="s">
         <v>67</v>
       </c>
@@ -3507,13 +3541,13 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B59" s="6"/>
+      <c r="B59" s="13"/>
       <c r="C59" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B60" s="6"/>
+      <c r="B60" s="13"/>
       <c r="C60" s="4" t="s">
         <v>69</v>
       </c>
@@ -3522,7 +3556,7 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B61" s="6"/>
+      <c r="B61" s="13"/>
       <c r="C61" s="4" t="s">
         <v>70</v>
       </c>
@@ -3862,7 +3896,7 @@
     </row>
     <row r="125" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A125" s="5"/>
-      <c r="B125" s="8"/>
+      <c r="B125" s="7"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B126" s="4"/>
@@ -3999,95 +4033,36 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1E4E7D2-C400-4FA7-B4EE-FE9CDA191CED}">
-  <dimension ref="A2:G11"/>
-  <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E623062-DF9A-4955-880A-5A9D00F54D06}">
+  <dimension ref="A2:B6"/>
+  <sheetFormatPr defaultRowHeight="27" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="15.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="29.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="124.25" style="10" customWidth="1"/>
-    <col min="5" max="5" width="105.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="70.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="E4" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="E5" s="9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A8" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="E9" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A2" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A3" s="14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A5" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A6" s="14" t="s">
+        <v>147</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4096,6 +4071,103 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1E4E7D2-C400-4FA7-B4EE-FE9CDA191CED}">
+  <dimension ref="A2:G11"/>
+  <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="15.375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="29.375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="124.25" style="9" customWidth="1"/>
+    <col min="5" max="5" width="105.75" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A3" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E4" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E5" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A8" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E9" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A55F660C-EF88-4090-AD81-2A0B2E837B2C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4106,7 +4178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32871931-A659-4325-B8EE-1625B1A3CB77}">
   <dimension ref="A1:H225"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4170,7 +4242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E919AACA-485F-464F-B192-8B7CCA645328}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>

--- a/wonderBoy.xlsx
+++ b/wonderBoy.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\250616JY\Github\wonderboy2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DC1B57-BF2F-450A-A746-9048B01775D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1943B5-2220-4CD5-8EE0-FF38719EC3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{196A970C-7FE6-4DB0-BC1D-10637FB7CC4F}"/>
   </bookViews>
   <sheets>
     <sheet name="게임 구성" sheetId="4" r:id="rId1"/>
-    <sheet name="UI_Item" sheetId="6" r:id="rId2"/>
-    <sheet name="PlayerPrefs" sheetId="5" r:id="rId3"/>
-    <sheet name="화면설정" sheetId="2" r:id="rId4"/>
-    <sheet name="wonderBoy" sheetId="1" r:id="rId5"/>
-    <sheet name="Message" sheetId="3" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId2"/>
+    <sheet name="UI_Item" sheetId="6" r:id="rId3"/>
+    <sheet name="PlayerPrefs" sheetId="5" r:id="rId4"/>
+    <sheet name="화면설정" sheetId="2" r:id="rId5"/>
+    <sheet name="wonderBoy" sheetId="1" r:id="rId6"/>
+    <sheet name="Message" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="160">
   <si>
     <t>최초 게임 설정</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -559,6 +560,48 @@
   </si>
   <si>
     <t>UI Item01 슬롯창에서 보유하고 있는 아이템을 그려줄 IMG Sprite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 게임을 시작하면 "InsertCoin"이 깜빡 거리면서 Coin 충전 대기 화면이 나온다 -&gt; Menu01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Insert Coin Txt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreditTxt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Credit 코인 들어왔을때 씬 전환 처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UIManagerOne.cs </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Insert Coin 깜빡거림 처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">코인 삽입 버튼 이벤트 처리 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>싱글톤으로 어디서든 사용가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공통으로 관리할 코인 관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlaterPrefs로 코인값을 얻어오고 조정함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 코인을 넣으면 Menu01 씬에서 Menu02 씬으로 전환</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -678,14 +721,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -842,6 +885,99 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>698</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>86212</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3B2A9A7-C93D-4ED7-828E-0753FA417C8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="485775" y="714375"/>
+          <a:ext cx="5001323" cy="3486637"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>276959</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>57637</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D1BD21C-E35A-4553-A8C3-CCF586171E0F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="504825" y="7372350"/>
+          <a:ext cx="5258534" cy="3486637"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1628,7 +1764,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2504,7 +2640,7 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">81 542 22 0 0,'0'0'850'0'0,"-8"1"-291"0"0,-20 3-431 0 0,1 0 2415 0 0,9-1 3696 0 0,92 9-6381 0 0,4-9-83 0 0,108-1 225 0 0,-178-2-43 0 0,-2 2-109 0 0,16 5 141 0 0,-22-7 11 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-2 8 4 0 0,0 1 0 0 0,-75 183 21 0 0,21-59-14 0 0,20-43-1 0 0,35-90-18 0 0,-5 14-1967 0 0,0 1 1 0 0,-14 20 0 0 0,15-38 306 0 0,-23-8-229 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="326.9">3 884 262 0 0,'3'-4'423'0'0,"2"-2"-247"0"0,0 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,11 0 0 0 0,39-3 211 0 0,3 5-150 0 0,1 5-72 0 0,27 2-139 0 0,-80-7-289 0 0,0 0-157 0 0,24 1-145 0 0,-24-2-95 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="326.89">3 884 262 0 0,'3'-4'423'0'0,"2"-2"-247"0"0,0 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,11 0 0 0 0,39-3 211 0 0,3 5-150 0 0,1 5-72 0 0,27 2-139 0 0,-80-7-289 0 0,0 0-157 0 0,24 1-145 0 0,-24-2-95 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="655.75">486 337 54 0 0,'-3'-6'443'0'0,"1"2"-868"0"0,-14-32 3349 0 0,13 28-1074 0 0,13 25-1388 0 0,3 15-212 0 0,-1 1 0 0 0,-2 0 0 0 0,-1 0 0 0 0,-2 1-1 0 0,4 35 1 0 0,11 49 346 0 0,20 69 27 0 0,70 255-512 0 0,-108-417-936 0 0,-4-25 800 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-3-3-57 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,-2-5-1 0 0,-4-5 262 0 0,1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,1-1-1 0 0,1-1 1 0 0,0 1-1 0 0,1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0-1 1 0 0,8-28-1 0 0,-8 41-129 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,7-4 0 0 0,0 1-86 0 0,0 1 1 0 0,1 0 0 0 0,18-7 0 0 0,31-15-3051 0 0,-55 25 2698 0 0,-3 1 190 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,2-3-1 0 0,16-19-2152 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1074.47">924 333 480 0 0,'-15'-44'3806'0'0,"14"41"-904"0"0,3 6-2526 0 0,5 10-149 0 0,-2-1 0 0 0,1 1 0 0 0,-2 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,-1-1 0 0 0,1 25 0 0 0,4 14 321 0 0,14 131 256 0 0,-5-29-693 0 0,-9-88-76 0 0,-6-61-7 0 0,-1-4-24 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,2 0-3 0 0,-1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-2 1 0 0,-31-36-15 0 0,18 17 61 0 0,2 0-1 0 0,1-1 1 0 0,0 0 0 0 0,2-1 0 0 0,0 0 0 0 0,2 0 0 0 0,0-1-1 0 0,-3-30 1 0 0,8 41-76 0 0,2 0 0 0 0,-1-1 0 0 0,2 1 0 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,12-14 0 0 0,-10 10 183 0 0,-6 10-127 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,8-5 0 0 0,14 0-51 0 0,-21 6 96 0 0,1 4-158 0 0,-2 0 70 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 2-1 0 0,0-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,2 6 1 0 0,9 24 197 0 0,-9-23-142 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 27 0 0 0,-3-19-35 0 0,-1 1-1 0 0,-1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,-2 0-1 0 0,0 0 1 0 0,-12 31 0 0 0,14-49-10 0 0,-65 147-414 0 0,65-147 403 0 0,0 1-11 0 0,-5 4-69 0 0,8-21 7 0 0,-1 9 111 0 0,1 1-25 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,5-2 0 0 0,-3 1-4 0 0,8-5 0 0 0,1 1 0 0 0,0 1-1 0 0,0 0 1 0 0,21-6-1 0 0,-28 11-14 0 0,0-1-144 0 0,64-10-3052 0 0,-63 11 2257 0 0,-4-2-17 0 0,0 0 472 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,3-5-1 0 0,-4 5-891 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1417.54">1263 640 222 0 0,'-2'-3'468'0'0,"0"1"-270"0"0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 1 0 0,1-3-1 0 0,0 1-34 0 0,3 1-22 0 0,66-33 96 0 0,-66 34-426 0 0,-1-1 47 0 0,16-8-227 0 0,-16 8-75 0 0,1-1-3 0 0,12-10 7 0 0,-13 10 32 0 0,-3 1 58 0 0,0 2 431 0 0,11-44-1249 0 0,-11 29 4371 0 0,18 233-1722 0 0,-13-116-2211 0 0,-6-68-569 0 0,0-28 449 0 0</inkml:trace>
@@ -3219,7 +3355,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="15" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -3230,7 +3366,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="13"/>
+      <c r="A5" s="15"/>
       <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
@@ -3239,7 +3375,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A6" s="13"/>
+      <c r="A6" s="15"/>
       <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
@@ -3248,7 +3384,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A7" s="13"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -3257,25 +3393,25 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="13"/>
+      <c r="A8" s="15"/>
       <c r="M8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A9" s="13"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A10" s="13"/>
+      <c r="A10" s="15"/>
       <c r="M10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11" s="13"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
@@ -3494,7 +3630,7 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="15" t="s">
         <v>71</v>
       </c>
       <c r="C54" s="4" t="s">
@@ -3505,7 +3641,7 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B55" s="13"/>
+      <c r="B55" s="15"/>
       <c r="C55" s="4" t="s">
         <v>64</v>
       </c>
@@ -3514,7 +3650,7 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B56" s="13"/>
+      <c r="B56" s="15"/>
       <c r="C56" s="4" t="s">
         <v>65</v>
       </c>
@@ -3523,7 +3659,7 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B57" s="13"/>
+      <c r="B57" s="15"/>
       <c r="C57" s="4" t="s">
         <v>66</v>
       </c>
@@ -3532,7 +3668,7 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B58" s="13"/>
+      <c r="B58" s="15"/>
       <c r="C58" s="4" t="s">
         <v>67</v>
       </c>
@@ -3541,13 +3677,13 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B59" s="13"/>
+      <c r="B59" s="15"/>
       <c r="C59" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B60" s="13"/>
+      <c r="B60" s="15"/>
       <c r="C60" s="4" t="s">
         <v>69</v>
       </c>
@@ -3556,7 +3692,7 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B61" s="13"/>
+      <c r="B61" s="15"/>
       <c r="C61" s="4" t="s">
         <v>70</v>
       </c>
@@ -4028,39 +4164,118 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55F84C0A-1CAA-4F04-9C70-E2C86345E238}">
+  <dimension ref="A2:D42"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B27" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B28" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="D34" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="D35" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B37" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="D38" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="D39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E623062-DF9A-4955-880A-5A9D00F54D06}">
   <dimension ref="A2:B6"/>
   <sheetFormatPr defaultRowHeight="27" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="70.375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="14"/>
+    <col min="1" max="1" width="70.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="13" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>147</v>
       </c>
     </row>
@@ -4070,7 +4285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1E4E7D2-C400-4FA7-B4EE-FE9CDA191CED}">
   <dimension ref="A2:G11"/>
   <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.15"/>
@@ -4167,7 +4382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A55F660C-EF88-4090-AD81-2A0B2E837B2C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4178,7 +4393,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32871931-A659-4325-B8EE-1625B1A3CB77}">
   <dimension ref="A1:H225"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4242,7 +4457,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E919AACA-485F-464F-B192-8B7CCA645328}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>

--- a/wonderBoy.xlsx
+++ b/wonderBoy.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\250616JY\Github\wonderboy2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1943B5-2220-4CD5-8EE0-FF38719EC3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F2BF19-3FBF-46D2-87AA-C81B3DA99CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{196A970C-7FE6-4DB0-BC1D-10637FB7CC4F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{196A970C-7FE6-4DB0-BC1D-10637FB7CC4F}"/>
   </bookViews>
   <sheets>
     <sheet name="게임 구성" sheetId="4" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="7" r:id="rId2"/>
-    <sheet name="UI_Item" sheetId="6" r:id="rId3"/>
-    <sheet name="PlayerPrefs" sheetId="5" r:id="rId4"/>
-    <sheet name="화면설정" sheetId="2" r:id="rId5"/>
-    <sheet name="wonderBoy" sheetId="1" r:id="rId6"/>
-    <sheet name="Message" sheetId="3" r:id="rId7"/>
+    <sheet name="Sheet2" sheetId="8" r:id="rId3"/>
+    <sheet name="UI_Item" sheetId="6" r:id="rId4"/>
+    <sheet name="PlayerPrefs" sheetId="5" r:id="rId5"/>
+    <sheet name="화면설정" sheetId="2" r:id="rId6"/>
+    <sheet name="wonderBoy" sheetId="1" r:id="rId7"/>
+    <sheet name="Message" sheetId="3" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="166">
   <si>
     <t>최초 게임 설정</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -602,6 +603,30 @@
   </si>
   <si>
     <t>2. 코인을 넣으면 Menu01 씬에서 Menu02 씬으로 전환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sowrd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모래시계</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4248,6 +4273,47 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B4F76D-7C39-40DD-8AB5-6FA1EAA653FC}">
+  <dimension ref="A3:A8"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E623062-DF9A-4955-880A-5A9D00F54D06}">
   <dimension ref="A2:B6"/>
   <sheetFormatPr defaultRowHeight="27" x14ac:dyDescent="0.15"/>
@@ -4285,7 +4351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1E4E7D2-C400-4FA7-B4EE-FE9CDA191CED}">
   <dimension ref="A2:G11"/>
   <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.15"/>
@@ -4382,7 +4448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A55F660C-EF88-4090-AD81-2A0B2E837B2C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4393,7 +4459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32871931-A659-4325-B8EE-1625B1A3CB77}">
   <dimension ref="A1:H225"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4457,7 +4523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E919AACA-485F-464F-B192-8B7CCA645328}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
